--- a/work/薪資計算_2026-04-25.xlsx
+++ b/work/薪資計算_2026-04-25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="2512" sheetId="2" r:id="rId1"/>
@@ -14,13 +14,14 @@
     <sheet name="2604" sheetId="5" r:id="rId5"/>
     <sheet name="2605" sheetId="6" r:id="rId6"/>
     <sheet name="2606" sheetId="8" r:id="rId7"/>
+    <sheet name="2607" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="15">
   <si>
     <t>工時</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,6 +76,10 @@
   </si>
   <si>
     <t>2026年 6月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年 7月</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +139,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -160,6 +165,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -486,13 +509,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
@@ -690,13 +713,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
@@ -1122,13 +1145,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
@@ -1415,23 +1438,23 @@
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="4">
-        <f>COUNT(B7:B16)</f>
-        <v>10</v>
+        <f>COUNT(B3:B16)</f>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1">
-        <f>SUM(D7:D16)</f>
-        <v>96</v>
-      </c>
-      <c r="E17" s="5">
-        <f>SUM(E7:E16)</f>
-        <v>9</v>
+        <f>SUM(D3:D16)</f>
+        <v>132</v>
+      </c>
+      <c r="E17" s="20">
+        <f t="shared" ref="E17:F17" si="2">SUM(E3:E16)</f>
+        <v>12</v>
       </c>
       <c r="F17" s="8">
-        <f>SUM(F7:F16)</f>
-        <v>17052</v>
+        <f t="shared" si="2"/>
+        <v>23520</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -1459,13 +1482,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="7" t="s">
@@ -1906,13 +1929,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="9" t="s">
@@ -2228,11 +2251,11 @@
         <v>8</v>
       </c>
       <c r="E18" s="14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="8">
         <f t="shared" si="3"/>
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="19" spans="2:6">
@@ -2247,11 +2270,11 @@
         <v>8</v>
       </c>
       <c r="E19" s="6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="8">
         <f t="shared" si="3"/>
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="20" spans="2:6">
@@ -2287,11 +2310,11 @@
       </c>
       <c r="E21" s="12">
         <f>SUM(E3:E20)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" s="8">
         <f>SUM(F3:F20)</f>
-        <v>19208</v>
+        <v>19404</v>
       </c>
     </row>
   </sheetData>
@@ -2306,7 +2329,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:F19"/>
+  <dimension ref="B1:F16"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="2.77734375" customWidth="1"/>
@@ -2315,13 +2338,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="10" t="s">
@@ -2348,15 +2371,15 @@
         <v>13</v>
       </c>
       <c r="D3" s="14">
-        <f t="shared" ref="D3:D18" si="0">21-C3</f>
+        <f t="shared" ref="D3:D15" si="0">21-C3</f>
         <v>8</v>
       </c>
       <c r="E3" s="14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" ref="F3:F18" si="1">(D3-E3)*196</f>
-        <v>1372</v>
+        <f t="shared" ref="F3:F15" si="1">(D3-E3)*196</f>
+        <v>1470</v>
       </c>
     </row>
     <row r="4" spans="2:6">
@@ -2370,12 +2393,12 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E4" s="6">
-        <v>1</v>
+      <c r="E4" s="15">
+        <v>0.5</v>
       </c>
       <c r="F4" s="8">
         <f t="shared" si="1"/>
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -2389,12 +2412,12 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E5" s="6">
-        <v>1</v>
+      <c r="E5" s="15">
+        <v>0.5</v>
       </c>
       <c r="F5" s="8">
         <f t="shared" si="1"/>
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="6" spans="2:6">
@@ -2465,12 +2488,12 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E9" s="6">
-        <v>1</v>
+      <c r="E9" s="15">
+        <v>0.5</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="1"/>
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="10" spans="2:6">
@@ -2484,36 +2507,36 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E10" s="6">
-        <v>1</v>
+      <c r="E10" s="15">
+        <v>0.5</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="1"/>
-        <v>1372</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="2">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="C11" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" s="14">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" s="6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="8">
         <f t="shared" si="1"/>
-        <v>1372</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="2">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="C12" s="14">
         <v>17</v>
@@ -2532,137 +2555,80 @@
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="2">
-        <v>46163</v>
-      </c>
-      <c r="C13" s="14">
+        <v>46169</v>
+      </c>
+      <c r="C13" s="16">
         <v>13</v>
       </c>
-      <c r="D13" s="14">
-        <f t="shared" si="0"/>
+      <c r="D13" s="16">
+        <f t="shared" ref="D13:D14" si="2">21-C13</f>
         <v>8</v>
       </c>
-      <c r="E13" s="6">
-        <v>1</v>
+      <c r="E13" s="16">
+        <v>0.5</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="1"/>
-        <v>1372</v>
+        <f t="shared" ref="F13:F14" si="3">(D13-E13)*196</f>
+        <v>1470</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" s="2">
-        <v>46164</v>
-      </c>
-      <c r="C14" s="14">
-        <v>17</v>
-      </c>
-      <c r="D14" s="14">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
+        <v>46171</v>
+      </c>
+      <c r="C14" s="18">
+        <v>13</v>
+      </c>
+      <c r="D14" s="18">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E14" s="18">
+        <v>0.5</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="1"/>
-        <v>784</v>
+        <f t="shared" si="3"/>
+        <v>1470</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="2">
-        <v>46167</v>
+        <v>46172</v>
       </c>
       <c r="C15" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E15" s="15">
+        <v>1</v>
       </c>
       <c r="F15" s="8">
         <f t="shared" si="1"/>
-        <v>784</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="2">
-        <v>46168</v>
-      </c>
-      <c r="C16" s="14">
-        <v>17</v>
-      </c>
-      <c r="D16" s="14">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
+      <c r="B16" s="4">
+        <f>COUNT(B3:B15)</f>
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="10">
+        <f>SUM(D3:D15)</f>
+        <v>100</v>
+      </c>
+      <c r="E16" s="14">
+        <f t="shared" ref="E16:F16" si="4">SUM(E3:E15)</f>
+        <v>7</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="1"/>
-        <v>784</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="2">
-        <v>46169</v>
-      </c>
-      <c r="C17" s="14">
-        <v>13</v>
-      </c>
-      <c r="D17" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <f t="shared" si="1"/>
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="2">
-        <v>46171</v>
-      </c>
-      <c r="C18" s="14">
-        <v>13</v>
-      </c>
-      <c r="D18" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="1"/>
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="4">
-        <f>COUNT(B3:B18)</f>
-        <v>16</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="10">
-        <f>SUM(D3:D18)</f>
-        <v>112</v>
-      </c>
-      <c r="E19" s="14">
-        <f t="shared" ref="E19:F19" si="2">SUM(E3:E18)</f>
-        <v>11</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="2"/>
-        <v>19796</v>
+        <f t="shared" si="4"/>
+        <v>18228</v>
       </c>
     </row>
   </sheetData>
@@ -2686,13 +2652,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="14" t="s">
@@ -2713,202 +2679,568 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="2">
-        <v>46174</v>
-      </c>
-      <c r="C3" s="14">
+        <v>46175</v>
+      </c>
+      <c r="C3" s="17">
         <v>13</v>
       </c>
-      <c r="D3" s="14">
-        <f t="shared" ref="D3:D7" si="0">21-C3</f>
+      <c r="D3" s="17">
+        <f t="shared" ref="D3" si="0">21-C3</f>
         <v>8</v>
       </c>
-      <c r="E3" s="14">
-        <v>1</v>
+      <c r="E3" s="17">
+        <v>0.5</v>
       </c>
       <c r="F3" s="8">
-        <f t="shared" ref="F3:F7" si="1">(D3-E3)*196</f>
-        <v>1372</v>
+        <f t="shared" ref="F3" si="1">(D3-E3)*196</f>
+        <v>1470</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="2">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="C4" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f t="shared" ref="D4:D19" si="2">21-C4</f>
+        <v>4</v>
       </c>
       <c r="E4" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="8">
-        <f t="shared" si="1"/>
-        <v>1372</v>
+        <f t="shared" ref="F4:F19" si="3">(D4-E4)*196</f>
+        <v>784</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="2">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="C5" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="14">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="E5" s="6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="1"/>
-        <v>784</v>
+        <f t="shared" si="3"/>
+        <v>1470</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="2">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="C6" s="14">
-        <v>13</v>
-      </c>
-      <c r="D6" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="D6" s="19">
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="E6" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="8">
-        <f t="shared" si="1"/>
-        <v>1372</v>
+        <f t="shared" si="3"/>
+        <v>784</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="2">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="C7" s="14">
         <v>17</v>
       </c>
-      <c r="D7" s="14">
-        <f t="shared" si="0"/>
+      <c r="D7" s="19">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
       </c>
       <c r="F7" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>784</v>
       </c>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="2"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="8"/>
+      <c r="B8" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C8" s="14">
+        <v>15</v>
+      </c>
+      <c r="D8" s="14">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="3"/>
+        <v>1078</v>
+      </c>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="2"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="8"/>
+      <c r="B9" s="2">
+        <v>46187</v>
+      </c>
+      <c r="C9" s="14">
+        <v>15</v>
+      </c>
+      <c r="D9" s="14">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="3"/>
+        <v>1078</v>
+      </c>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="2"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="8"/>
+      <c r="B10" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C10" s="14">
+        <v>17</v>
+      </c>
+      <c r="D10" s="14">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="2"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="8"/>
+      <c r="B11" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C11" s="14">
+        <v>17</v>
+      </c>
+      <c r="D11" s="14">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="2"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="B12" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C12" s="14">
+        <v>11</v>
+      </c>
+      <c r="D12" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <f t="shared" si="3"/>
+        <v>1764</v>
+      </c>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="2"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
+      <c r="B13" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C13" s="14">
+        <v>17</v>
+      </c>
+      <c r="D13" s="14">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="2"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="8"/>
+      <c r="B14" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C14" s="14">
+        <v>11</v>
+      </c>
+      <c r="D14" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="3"/>
+        <v>1764</v>
+      </c>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="2"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="8"/>
+      <c r="B15" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C15" s="14">
+        <v>11</v>
+      </c>
+      <c r="D15" s="14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <f t="shared" si="3"/>
+        <v>1764</v>
+      </c>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="2"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C16" s="19">
+        <v>17</v>
+      </c>
+      <c r="D16" s="19">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="3"/>
+        <v>784</v>
+      </c>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="2"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="8"/>
+      <c r="B17" s="2">
+        <v>46200</v>
+      </c>
+      <c r="C17" s="19">
+        <v>15</v>
+      </c>
+      <c r="D17" s="19">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="8">
+        <f t="shared" si="3"/>
+        <v>1078</v>
+      </c>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="2"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="8"/>
+      <c r="B18" s="2">
+        <v>46201</v>
+      </c>
+      <c r="C18" s="19">
+        <v>15</v>
+      </c>
+      <c r="D18" s="19">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="3"/>
+        <v>1078</v>
+      </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="2"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="8"/>
+      <c r="B19" s="2">
+        <v>46202</v>
+      </c>
+      <c r="C19" s="19">
+        <v>11</v>
+      </c>
+      <c r="D19" s="19">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="3"/>
+        <v>1764</v>
+      </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="4">
         <f>COUNT(B3:B19)</f>
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="14">
         <f>SUM(D3:D19)</f>
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="E20" s="14">
-        <f t="shared" ref="E20:F20" si="2">SUM(E3:E19)</f>
+        <f>SUM(E3:E19)</f>
+        <v>7</v>
+      </c>
+      <c r="F20" s="8">
+        <f>SUM(F3:F19)</f>
+        <v>19796</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:F20"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="2.77734375" customWidth="1"/>
+    <col min="2" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6">
+      <c r="B1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="2:6">
+      <c r="B2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C3" s="19">
+        <v>15</v>
+      </c>
+      <c r="D3" s="19">
+        <f t="shared" ref="D3:D5" si="0">21-C3</f>
+        <v>6</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="8">
+        <f t="shared" ref="F3:F5" si="1">(D3-E3)*196</f>
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C4" s="19">
+        <v>11</v>
+      </c>
+      <c r="D4" s="19">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" si="1"/>
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C5" s="19">
+        <v>15</v>
+      </c>
+      <c r="D5" s="19">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="1"/>
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="2"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="2"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="2"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="2"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="2"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="2"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="2"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="2"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="2"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="2"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="2"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="2"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="2"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="2"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="4">
+        <f>COUNT(B3:B19)</f>
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="19">
+        <f>SUM(D3:D19)</f>
+        <v>22</v>
+      </c>
+      <c r="E20" s="19">
+        <f>SUM(E3:E19)</f>
+        <v>2</v>
+      </c>
       <c r="F20" s="8">
-        <f t="shared" si="2"/>
-        <v>5684</v>
+        <f>SUM(F3:F19)</f>
+        <v>3920</v>
       </c>
     </row>
   </sheetData>
